--- a/nr-add-lipids/ig/StructureDefinition-mesures-original-value.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-original-value.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-19T09:23:14+00:00</t>
+    <t>2026-01-19T09:39:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-original-value.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-original-value.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-19T09:39:10+00:00</t>
+    <t>2026-01-19T09:47:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-original-value.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-original-value.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-19T09:47:31+00:00</t>
+    <t>2026-01-19T09:54:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-original-value.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-original-value.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-19T09:54:18+00:00</t>
+    <t>2026-01-19T09:56:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-original-value.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-original-value.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-19T09:56:13+00:00</t>
+    <t>2026-01-19T10:07:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-original-value.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-original-value.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-19T10:07:50+00:00</t>
+    <t>2026-01-20T07:44:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-original-value.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-original-value.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-20T07:44:39+00:00</t>
+    <t>2026-01-20T09:11:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-original-value.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-original-value.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-20T09:11:57+00:00</t>
+    <t>2026-01-20T09:43:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-original-value.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-original-value.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-20T09:43:53+00:00</t>
+    <t>2026-01-20T09:47:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-original-value.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-original-value.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-20T09:47:48+00:00</t>
+    <t>2026-01-20T10:06:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-original-value.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-original-value.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-20T10:06:11+00:00</t>
+    <t>2026-01-20T11:11:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
